--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2018/American_Aircraft_Cumulative_Statistics_2018.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2018/American_Aircraft_Cumulative_Statistics_2018.xlsx
@@ -13,36 +13,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="28" uniqueCount="28">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -124,10 +142,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -147,40 +165,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -188,40 +206,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>4716719809</v>
+        <v>1162952805</v>
       </c>
       <c r="C2" s="0">
-        <v>5564631629</v>
+        <v>1496926572</v>
       </c>
       <c r="D2" s="0">
-        <v>287578</v>
+        <v>209948</v>
       </c>
       <c r="E2" s="0">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>27189</v>
+        <v>33678</v>
       </c>
       <c r="G2" s="0">
-        <v>1.4099999999999999</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="H2" s="0">
-        <v>4.9199999999999999</v>
+        <v>8.0700000000000003</v>
       </c>
       <c r="I2" s="0">
-        <v>84.760000000000005</v>
+        <v>77.689999999999998</v>
       </c>
       <c r="J2" s="0">
-        <v>1374</v>
+        <v>449</v>
       </c>
       <c r="K2" s="0">
-        <v>9551</v>
+        <v>2482.6500000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>64.099999999999994</v>
+        <v>25.079999999999998</v>
       </c>
       <c r="M2" s="0">
-        <v>0.16</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -229,40 +247,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6220285029</v>
+        <v>14621552952</v>
       </c>
       <c r="C3" s="0">
-        <v>7450905732</v>
+        <v>17790970088</v>
       </c>
       <c r="D3" s="0">
-        <v>530691</v>
+        <v>398722</v>
       </c>
       <c r="E3" s="0">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F3" s="0">
-        <v>47994</v>
+        <v>179558</v>
       </c>
       <c r="G3" s="0">
-        <v>3.4199999999999999</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="H3" s="0">
-        <v>7.7199999999999998</v>
+        <v>9.0999999999999996</v>
       </c>
       <c r="I3" s="0">
-        <v>83.480000000000004</v>
+        <v>82.189999999999998</v>
       </c>
       <c r="J3" s="0">
-        <v>861</v>
+        <v>774</v>
       </c>
       <c r="K3" s="0">
-        <v>3923</v>
+        <v>3594.7600000000002</v>
       </c>
       <c r="L3" s="0">
-        <v>21.760000000000002</v>
+        <v>28.079999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="4">
@@ -297,13 +315,13 @@
         <v>840</v>
       </c>
       <c r="K4" s="0">
-        <v>4074</v>
+        <v>4073.7399999999998</v>
       </c>
       <c r="L4" s="0">
         <v>27.16</v>
       </c>
       <c r="M4" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="5">
@@ -311,40 +329,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>9840429795</v>
+        <v>52401582830</v>
       </c>
       <c r="C5" s="0">
-        <v>11686120786</v>
+        <v>60955298254</v>
       </c>
       <c r="D5" s="0">
-        <v>523572</v>
+        <v>776996</v>
       </c>
       <c r="E5" s="0">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="F5" s="0">
-        <v>80006</v>
+        <v>265599</v>
       </c>
       <c r="G5" s="0">
-        <v>3.5800000000000001</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>9.1300000000000008</v>
+        <v>11.23</v>
       </c>
       <c r="I5" s="0">
-        <v>84.209999999999994</v>
+        <v>85.969999999999999</v>
       </c>
       <c r="J5" s="0">
-        <v>927</v>
+        <v>1293</v>
       </c>
       <c r="K5" s="0">
-        <v>4332</v>
+        <v>5100.6300000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>27.48</v>
+        <v>28.66</v>
       </c>
       <c r="M5" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="6">
@@ -352,40 +370,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>7411459308</v>
+        <v>54703636843</v>
       </c>
       <c r="C6" s="0">
-        <v>8684536092</v>
+        <v>65135126527</v>
       </c>
       <c r="D6" s="0">
-        <v>1069524</v>
+        <v>597570</v>
       </c>
       <c r="E6" s="0">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="F6" s="0">
-        <v>44092</v>
+        <v>387937</v>
       </c>
       <c r="G6" s="0">
-        <v>5.4299999999999997</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>15.51</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>85.340000000000003</v>
+        <v>83.980000000000004</v>
       </c>
       <c r="J6" s="0">
-        <v>1094</v>
+        <v>1047</v>
       </c>
       <c r="K6" s="0">
-        <v>2946</v>
+        <v>4344.0799999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>16.359999999999999</v>
+        <v>27.100000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="7">
@@ -393,40 +411,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>27929614176</v>
+        <v>1854492984</v>
       </c>
       <c r="C7" s="0">
-        <v>33288082466</v>
+        <v>2148309026</v>
       </c>
       <c r="D7" s="0">
-        <v>701540</v>
+        <v>541136</v>
       </c>
       <c r="E7" s="0">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="F7" s="0">
-        <v>186116</v>
+        <v>10596</v>
       </c>
       <c r="G7" s="0">
-        <v>3.9199999999999999</v>
+        <v>2.6699999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>11.949999999999999</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="I7" s="0">
-        <v>83.900000000000006</v>
+        <v>86.319999999999993</v>
       </c>
       <c r="J7" s="0">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="K7" s="0">
-        <v>4286</v>
+        <v>5108.4200000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>28.370000000000001</v>
+        <v>29.699999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="8">
@@ -434,40 +452,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>15037177980</v>
+        <v>6668901074</v>
       </c>
       <c r="C8" s="0">
-        <v>17871325258</v>
+        <v>7919717336</v>
       </c>
       <c r="D8" s="0">
-        <v>826993</v>
+        <v>671162</v>
       </c>
       <c r="E8" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F8" s="0">
-        <v>97496</v>
+        <v>23616</v>
       </c>
       <c r="G8" s="0">
-        <v>4.5099999999999998</v>
+        <v>2</v>
       </c>
       <c r="H8" s="0">
-        <v>12.08</v>
+        <v>8.9000000000000004</v>
       </c>
       <c r="I8" s="0">
-        <v>84.140000000000001</v>
+        <v>84.209999999999994</v>
       </c>
       <c r="J8" s="0">
-        <v>1017</v>
+        <v>1885</v>
       </c>
       <c r="K8" s="0">
-        <v>3534</v>
+        <v>5867.5600000000004</v>
       </c>
       <c r="L8" s="0">
-        <v>19.609999999999999</v>
+        <v>32.979999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="9">
@@ -475,40 +493,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>16470884916</v>
+        <v>5725736395</v>
       </c>
       <c r="C9" s="0">
-        <v>19144930800</v>
+        <v>7115204463</v>
       </c>
       <c r="D9" s="0">
-        <v>529744</v>
+        <v>854166</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="F9" s="0">
-        <v>127211</v>
+        <v>13732</v>
       </c>
       <c r="G9" s="0">
-        <v>3.52</v>
+        <v>1.6499999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>9.4700000000000006</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="I9" s="0">
-        <v>86.030000000000001</v>
+        <v>80.469999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>1003</v>
+        <v>2519</v>
       </c>
       <c r="K9" s="0">
-        <v>4600</v>
+        <v>7393.1099999999997</v>
       </c>
       <c r="L9" s="0">
-        <v>30.670000000000002</v>
+        <v>35.909999999999997</v>
       </c>
       <c r="M9" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="10">
@@ -516,40 +534,286 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>94571965159</v>
+        <v>5596779048</v>
       </c>
       <c r="C10" s="0">
-        <v>112018408909</v>
+        <v>7334087538</v>
       </c>
       <c r="D10" s="0">
-        <v>601506</v>
+        <v>1396969</v>
       </c>
       <c r="E10" s="0">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="F10" s="0">
-        <v>676160</v>
+        <v>9138</v>
       </c>
       <c r="G10" s="0">
-        <v>3.6299999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="H10" s="0">
+        <v>12.4</v>
+      </c>
+      <c r="I10" s="0">
+        <v>76.310000000000002</v>
+      </c>
+      <c r="J10" s="0">
+        <v>3307</v>
+      </c>
+      <c r="K10" s="0">
+        <v>8836.2000000000007</v>
+      </c>
+      <c r="L10" s="0">
+        <v>36.399999999999999</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="0">
-        <v>84.430000000000007</v>
-      </c>
-      <c r="J10" s="0">
-        <v>1041</v>
-      </c>
-      <c r="K10" s="0">
-        <v>4382</v>
-      </c>
-      <c r="L10" s="0">
-        <v>27.539999999999999</v>
-      </c>
-      <c r="M10" s="0">
-        <v>0.070000000000000007</v>
+      <c r="B11" s="0">
+        <v>3994377923</v>
+      </c>
+      <c r="C11" s="0">
+        <v>5376665677</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1751357</v>
+      </c>
+      <c r="E11" s="0">
+        <v>287</v>
+      </c>
+      <c r="F11" s="0">
+        <v>4913</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="H11" s="0">
+        <v>13.07</v>
+      </c>
+      <c r="I11" s="0">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="J11" s="0">
+        <v>3822</v>
+      </c>
+      <c r="K11" s="0">
+        <v>10147.58</v>
+      </c>
+      <c r="L11" s="0">
+        <v>35.439999999999998</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>7598671738</v>
+      </c>
+      <c r="C12" s="0">
+        <v>9426083150</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1388230</v>
+      </c>
+      <c r="E12" s="0">
+        <v>226</v>
+      </c>
+      <c r="F12" s="0">
+        <v>9717</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H12" s="0">
+        <v>12.51</v>
+      </c>
+      <c r="I12" s="0">
+        <v>80.609999999999999</v>
+      </c>
+      <c r="J12" s="0">
+        <v>4300</v>
+      </c>
+      <c r="K12" s="0">
+        <v>8440.7800000000007</v>
+      </c>
+      <c r="L12" s="0">
+        <v>37.409999999999997</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>9210929898</v>
+      </c>
+      <c r="C13" s="0">
+        <v>11634211555</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1975248</v>
+      </c>
+      <c r="E13" s="0">
+        <v>284</v>
+      </c>
+      <c r="F13" s="0">
+        <v>7342</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1.25</v>
+      </c>
+      <c r="H13" s="0">
+        <v>13.75</v>
+      </c>
+      <c r="I13" s="0">
+        <v>79.170000000000002</v>
+      </c>
+      <c r="J13" s="0">
+        <v>5574</v>
+      </c>
+      <c r="K13" s="0">
+        <v>10342.639999999999</v>
+      </c>
+      <c r="L13" s="0">
+        <v>36.380000000000003</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.071999999999999995</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>19559614671</v>
+      </c>
+      <c r="C14" s="0">
+        <v>24645586939</v>
+      </c>
+      <c r="D14" s="0">
+        <v>1530782</v>
+      </c>
+      <c r="E14" s="0">
+        <v>269</v>
+      </c>
+      <c r="F14" s="0">
+        <v>21550</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1.3400000000000001</v>
+      </c>
+      <c r="H14" s="0">
+        <v>11.59</v>
+      </c>
+      <c r="I14" s="0">
+        <v>79.359999999999999</v>
+      </c>
+      <c r="J14" s="0">
+        <v>4248</v>
+      </c>
+      <c r="K14" s="0">
+        <v>10760.52</v>
+      </c>
+      <c r="L14" s="0">
+        <v>39.969999999999999</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.081000000000000003</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>11203625434</v>
+      </c>
+      <c r="C15" s="0">
+        <v>14162132791</v>
+      </c>
+      <c r="D15" s="0">
+        <v>2003131</v>
+      </c>
+      <c r="E15" s="0">
+        <v>305</v>
+      </c>
+      <c r="F15" s="0">
+        <v>9319</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H15" s="0">
+        <v>13.210000000000001</v>
+      </c>
+      <c r="I15" s="0">
+        <v>79.109999999999999</v>
+      </c>
+      <c r="J15" s="0">
+        <v>4976</v>
+      </c>
+      <c r="K15" s="0">
+        <v>12428.83</v>
+      </c>
+      <c r="L15" s="0">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0.082000000000000003</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0">
+        <v>201248248741</v>
+      </c>
+      <c r="C16" s="0">
+        <v>243468196062</v>
+      </c>
+      <c r="D16" s="0">
+        <v>749894</v>
+      </c>
+      <c r="E16" s="0">
+        <v>165</v>
+      </c>
+      <c r="F16" s="0">
+        <v>1042751</v>
+      </c>
+      <c r="G16" s="0">
+        <v>3.21</v>
+      </c>
+      <c r="H16" s="0">
+        <v>10.390000000000001</v>
+      </c>
+      <c r="I16" s="0">
+        <v>82.659999999999997</v>
+      </c>
+      <c r="J16" s="0">
+        <v>1267</v>
+      </c>
+      <c r="K16" s="0">
+        <v>5513.8599999999997</v>
+      </c>
+      <c r="L16" s="0">
+        <v>30.809999999999999</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0.075999999999999998</v>
       </c>
     </row>
   </sheetData>
